--- a/tame_output/ON/bt/strategyON_20230806.xlsx
+++ b/tame_output/ON/bt/strategyON_20230806.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>103.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.0%</t>
+          <t>140.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-04</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>135.5%</t>
+          <t>135.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1680"/>
+  <dimension ref="A1:G1681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40150,7 +40150,7 @@
         <v>45142</v>
       </c>
       <c r="B1680" t="n">
-        <v>2.875118223650516</v>
+        <v>2.874873035510626</v>
       </c>
       <c r="C1680" t="n">
         <v>2.995458941041095</v>
@@ -40166,6 +40166,29 @@
       </c>
       <c r="G1680" t="n">
         <v>4.295375090175949</v>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" s="2" t="n">
+        <v>45143</v>
+      </c>
+      <c r="B1681" t="n">
+        <v>2.8735827581663</v>
+      </c>
+      <c r="C1681" t="n">
+        <v>2.994972051492215</v>
+      </c>
+      <c r="D1681" t="n">
+        <v>1.538138671206002</v>
+      </c>
+      <c r="E1681" t="n">
+        <v>3.609871095660869</v>
+      </c>
+      <c r="F1681" t="n">
+        <v>2.166511173764359</v>
+      </c>
+      <c r="G1681" t="n">
+        <v>4.294878755750832</v>
       </c>
     </row>
   </sheetData>
